--- a/feedback_forms/014_sports_equipment_usability_feedback_survey--feedback_forms.xlsx
+++ b/feedback_forms/014_sports_equipment_usability_feedback_survey--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>introduction</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,7 +538,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -548,10 +548,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Section 1</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>General Feedback</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please share your overall thoughts about the sports equipment.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -561,46 +565,54 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>section_1_1</t>
+          <t>section_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Subsection 1</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Ease of Use</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>How easy was it to use the equipment?</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>section_1_2</t>
+          <t>section_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Subsection 2</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Comfort</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>How comfortable did you find the equipment?</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,61 +624,73 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>section_2</t>
+          <t>section_4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Section 2</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>How would you rate the quality of the equipment?</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>section_2_1</t>
+          <t>section_5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Subsection 1</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Recommendation</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>How likely are you to recommend the equipment to others?</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>section_2_2</t>
+          <t>section_6</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Subsection 2</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Demographics</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Please answer the following questions about yourself.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -681,407 +705,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>section_2_3</t>
+          <t>section_8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Subsection 3</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Additional Comments</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Do you have any additional comments or suggestions?</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>section_3</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Section 3</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>section_3_1</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Subsection 1</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>section_3_2</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Subsection 2</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>section_4</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Section 4</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>section_4_1</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Subsection 1</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>section_4_2</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Subsection 2</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>section_5</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Section 5</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>section_5_1</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Subsection 1</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>section_6</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Section 6</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>section_6_1</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Subsection 1</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>section_7</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Section 7</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>section_7_1</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Subsection 1</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>section_8</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Section 8</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>section_8_1</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Subsection 1</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>section_9</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Section 9</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>section_9_1</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Subsection 1</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>submission</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Submission</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +735,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,119 +763,119 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>section_2_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'option_1'}</t>
+          <t>very_easy</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Option 1'}</t>
+          <t>Very Easy</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>section_2_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'option_2'}</t>
+          <t>somewhat_easy</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Option 2'}</t>
+          <t>Somewhat Easy</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>section_1_choices</t>
+          <t>section_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'option_3'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Option 3'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>section_1_2_choices</t>
+          <t>section_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>somewhat_hard</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Somewhat Hard</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>section_1_2_choices</t>
+          <t>section_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>very_hard</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Very Hard</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>section_2_choices</t>
+          <t>section_3_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'option_1'}</t>
+          <t>very_comfortable</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Option 1'}</t>
+          <t>Very Comfortable</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>section_2_choices</t>
+          <t>section_3_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'option_2'}</t>
+          <t>somewhat_comfortable</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Option 2'}</t>
+          <t>Somewhat Comfortable</t>
         </is>
       </c>
     </row>
@@ -1250,12 +887,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1267,148 +904,182 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>somewhat_uncomfortable</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Somewhat Uncomfortable</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>section_5_choices</t>
+          <t>section_3_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>very_uncomfortable</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Very Uncomfortable</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>section_5_choices</t>
+          <t>section_4_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>section_6_choices</t>
+          <t>section_4_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>section_6_choices</t>
+          <t>section_4_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>section_8_choices</t>
+          <t>section_4_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>section_8_choices</t>
+          <t>section_5_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>very_likely</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Very Likely</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>section_9_choices</t>
+          <t>section_5_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>somewhat_likely</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Somewhat Likely</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>section_9_choices</t>
+          <t>section_5_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>section_5_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>somewhat_unlikely</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Somewhat Unlikely</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>section_5_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>very_unlikely</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Very Unlikely</t>
         </is>
       </c>
     </row>
